--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_nuble.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_nuble.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:37</t>
+    <t xml:space="preserve">2026-09-09 19:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_nuble.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_nuble.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:55</t>
+    <t xml:space="preserve">2026-09-18 17:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_nuble.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_nuble.xlsx
@@ -30,69 +30,69 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Ñiquén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Nicolás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treguaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Carmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portezuelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninhue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coelemu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pemuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Fabián</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quirihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Carlos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yungay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ignacio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranquil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coihueco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chillán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobquecura</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chillán Viejo</t>
   </si>
   <si>
-    <t xml:space="preserve">Cobquecura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chillán</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coihueco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranquil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Ignacio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yungay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Carlos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quirihue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Fabián</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pinto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pemuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coelemu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ninhue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portezuelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Carmen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treguaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Nicolás</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ñiquén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:02</t>
+    <t xml:space="preserve">2026-09-27 21:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -522,13 +522,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>32910</v>
+        <v>13587</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>32735</v>
+        <v>11544</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>100.53</v>
+        <v>117.7</v>
       </c>
     </row>
     <row r="3">
@@ -536,13 +536,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5317</v>
+        <v>13684</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5286</v>
+        <v>11959</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>100.59</v>
+        <v>114.42</v>
       </c>
     </row>
     <row r="4">
@@ -550,13 +550,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>196390</v>
+        <v>6147</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>195042</v>
+        <v>5636</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>100.69</v>
+        <v>109.07</v>
       </c>
     </row>
     <row r="5">
@@ -564,13 +564,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>28209</v>
+        <v>13413</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>27914</v>
+        <v>12360</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>101.06</v>
+        <v>108.52</v>
       </c>
     </row>
     <row r="6">
@@ -578,13 +578,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6296</v>
+        <v>5318</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6212</v>
+        <v>4959</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>101.35</v>
+        <v>107.24</v>
       </c>
     </row>
     <row r="7">
@@ -592,13 +592,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>19008</v>
+        <v>23949</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>18426</v>
+        <v>22426</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>103.16</v>
+        <v>106.79</v>
       </c>
     </row>
     <row r="8">
@@ -606,13 +606,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>17145</v>
+        <v>5779</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>16568</v>
+        <v>5429</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>103.48</v>
+        <v>106.45</v>
       </c>
     </row>
     <row r="9">
@@ -620,13 +620,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>19048</v>
+        <v>17830</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>18398</v>
+        <v>16751</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>103.53</v>
+        <v>106.44</v>
       </c>
     </row>
     <row r="10">
@@ -634,13 +634,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>57829</v>
+        <v>9162</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>55608</v>
+        <v>8639</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>103.99</v>
+        <v>106.05</v>
       </c>
     </row>
     <row r="11">
@@ -648,13 +648,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>12614</v>
+        <v>12365</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>12115</v>
+        <v>11680</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>104.12</v>
+        <v>105.86</v>
       </c>
     </row>
     <row r="12">
@@ -676,13 +676,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>12365</v>
+        <v>12614</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>11680</v>
+        <v>12115</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>105.86</v>
+        <v>104.12</v>
       </c>
     </row>
     <row r="14">
@@ -690,13 +690,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>9162</v>
+        <v>57829</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>8639</v>
+        <v>55608</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>106.05</v>
+        <v>103.99</v>
       </c>
     </row>
     <row r="15">
@@ -704,13 +704,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>17830</v>
+        <v>19048</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>16751</v>
+        <v>18398</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>106.44</v>
+        <v>103.53</v>
       </c>
     </row>
     <row r="16">
@@ -718,13 +718,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>5779</v>
+        <v>17145</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5429</v>
+        <v>16568</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>106.45</v>
+        <v>103.48</v>
       </c>
     </row>
     <row r="17">
@@ -732,13 +732,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>23949</v>
+        <v>19008</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>22426</v>
+        <v>18426</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>106.79</v>
+        <v>103.16</v>
       </c>
     </row>
     <row r="18">
@@ -746,13 +746,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>5318</v>
+        <v>6296</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>4959</v>
+        <v>6212</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>107.24</v>
+        <v>101.35</v>
       </c>
     </row>
     <row r="19">
@@ -760,13 +760,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>13413</v>
+        <v>28209</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>12360</v>
+        <v>27914</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>108.52</v>
+        <v>101.06</v>
       </c>
     </row>
     <row r="20">
@@ -774,13 +774,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>6147</v>
+        <v>196390</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>5636</v>
+        <v>195042</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>109.07</v>
+        <v>100.69</v>
       </c>
     </row>
     <row r="21">
@@ -788,13 +788,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>13684</v>
+        <v>5317</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>11959</v>
+        <v>5286</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>114.42</v>
+        <v>100.59</v>
       </c>
     </row>
     <row r="22">
@@ -802,13 +802,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>13587</v>
+        <v>32910</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>11544</v>
+        <v>32735</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>117.7</v>
+        <v>100.53</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_nuble.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2018_nuble.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Quillón</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Coihueco</t>
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:44</t>
+    <t xml:space="preserve">2026-10-05 05:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
